--- a/data/Enquiry.xlsx
+++ b/data/Enquiry.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Hyundai\hyundai_dashboard_V7\hyundai_dashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC3AB594-F262-402A-8F90-35FDBEA9BD6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C6E927F-EB5B-4293-AD89-327F49C82644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -70705,6 +70705,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AS684" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
